--- a/macos/facility_studio/resources/Equipment_Template.xlsx
+++ b/macos/facility_studio/resources/Equipment_Template.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填寫說明" sheetId="1" r:id="Rff8c74e5c55c4493"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="電力" sheetId="2" r:id="R336edde2b4184f72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCW" sheetId="3" r:id="Re75d9c6d20ed4ba9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDA" sheetId="4" r:id="Rd689d976eb384490"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="N2" sheetId="5" r:id="R49cbac2293ea443e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EXHAUST" sheetId="6" r:id="Rfb63e0629a7b4f3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DI" sheetId="7" r:id="Rce03d628ccd84ba9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PV" sheetId="8" r:id="R904c204c88b04736"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填寫說明" sheetId="1" r:id="R441bc35e032444c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="電力" sheetId="2" r:id="R1a4424d21c334066"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCW" sheetId="3" r:id="R5515ae00b3f34972"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDA" sheetId="4" r:id="R75745cf33ca641fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="N2" sheetId="5" r:id="R83f3b60c751b42b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EXHAUST" sheetId="6" r:id="R5953b5a207734cc0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DI" sheetId="7" r:id="R6290b9aff7734a86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PV" sheetId="8" r:id="R0a4147711d164c50"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -138,7 +138,7 @@
         <x:color rgb="FFAF2D2D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFE4DF"/>
         </x:patternFill>
       </x:fill>
@@ -148,7 +148,7 @@
         <x:color rgb="FFAF2D2D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFE4DF"/>
         </x:patternFill>
       </x:fill>
@@ -158,7 +158,7 @@
         <x:color rgb="FFAF2D2D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFE4DF"/>
         </x:patternFill>
       </x:fill>
@@ -168,7 +168,7 @@
         <x:color rgb="FFAF2D2D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFE4DF"/>
         </x:patternFill>
       </x:fill>
@@ -178,7 +178,7 @@
         <x:color rgb="FFAF2D2D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFE4DF"/>
         </x:patternFill>
       </x:fill>
@@ -188,7 +188,7 @@
         <x:color rgb="FFAF2D2D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFE4DF"/>
         </x:patternFill>
       </x:fill>
@@ -198,7 +198,7 @@
         <x:color rgb="FFAF2D2D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFE4DF"/>
         </x:patternFill>
       </x:fill>
@@ -208,7 +208,7 @@
         <x:color rgb="FFAF2D2D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFE4DF"/>
         </x:patternFill>
       </x:fill>
@@ -218,7 +218,7 @@
         <x:color rgb="FFAF2D2D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFE4DF"/>
         </x:patternFill>
       </x:fill>
@@ -228,7 +228,7 @@
         <x:color rgb="FFAF2D2D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFE4DF"/>
         </x:patternFill>
       </x:fill>
@@ -238,7 +238,7 @@
         <x:color rgb="FFAF2D2D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFE4DF"/>
         </x:patternFill>
       </x:fill>
@@ -248,7 +248,7 @@
         <x:color rgb="FFAF2D2D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFE4DF"/>
         </x:patternFill>
       </x:fill>
@@ -258,7 +258,7 @@
         <x:color rgb="FFAF2D2D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFE4DF"/>
         </x:patternFill>
       </x:fill>
@@ -268,7 +268,7 @@
         <x:color rgb="FFAF2D2D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFE4DF"/>
         </x:patternFill>
       </x:fill>
@@ -278,7 +278,7 @@
         <x:color rgb="FFAF2D2D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFE4DF"/>
         </x:patternFill>
       </x:fill>
@@ -288,7 +288,7 @@
         <x:color rgb="FFAF2D2D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFE4DF"/>
         </x:patternFill>
       </x:fill>
@@ -298,7 +298,7 @@
         <x:color rgb="FFAF2D2D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFE4DF"/>
         </x:patternFill>
       </x:fill>
@@ -308,7 +308,7 @@
         <x:color rgb="FFAF2D2D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFE4DF"/>
         </x:patternFill>
       </x:fill>
@@ -318,7 +318,7 @@
         <x:color rgb="FFAF2D2D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFE4DF"/>
         </x:patternFill>
       </x:fill>
@@ -328,7 +328,7 @@
         <x:color rgb="FFAF2D2D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFE4DF"/>
         </x:patternFill>
       </x:fill>
@@ -338,7 +338,7 @@
         <x:color rgb="FFAF2D2D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFE4DF"/>
         </x:patternFill>
       </x:fill>
@@ -348,7 +348,7 @@
         <x:color rgb="FFAF2D2D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFE4DF"/>
         </x:patternFill>
       </x:fill>
@@ -358,7 +358,7 @@
         <x:color rgb="FFAF2D2D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFE4DF"/>
         </x:patternFill>
       </x:fill>
@@ -368,7 +368,7 @@
         <x:color rgb="FFAF2D2D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFE4DF"/>
         </x:patternFill>
       </x:fill>
@@ -378,7 +378,7 @@
         <x:color rgb="FFAF2D2D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFE4DF"/>
         </x:patternFill>
       </x:fill>
@@ -388,7 +388,7 @@
         <x:color rgb="FFAF2D2D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFE4DF"/>
         </x:patternFill>
       </x:fill>
@@ -398,7 +398,7 @@
         <x:color rgb="FFAF2D2D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFE4DF"/>
         </x:patternFill>
       </x:fill>
@@ -408,7 +408,7 @@
         <x:color rgb="FFAF2D2D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFE4DF"/>
         </x:patternFill>
       </x:fill>
@@ -418,7 +418,7 @@
         <x:color rgb="FFAF2D2D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFE4DF"/>
         </x:patternFill>
       </x:fill>
@@ -428,7 +428,7 @@
         <x:color rgb="FFAF2D2D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFE4DF"/>
         </x:patternFill>
       </x:fill>
@@ -438,7 +438,7 @@
         <x:color rgb="FFAF2D2D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFE4DF"/>
         </x:patternFill>
       </x:fill>
@@ -448,7 +448,7 @@
         <x:color rgb="FFAF2D2D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFE4DF"/>
         </x:patternFill>
       </x:fill>
@@ -458,7 +458,7 @@
         <x:color rgb="FFAF2D2D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFE4DF"/>
         </x:patternFill>
       </x:fill>
@@ -717,7 +717,7 @@
         <x:v>同時使用率</x:v>
       </x:c>
       <x:c r="B8" s="6" t="str">
-        <x:v>填0~100的瞬間同時需求係數。空白採100%。不能用每小時運轉比例替代安全系統的設計量。</x:v>
+        <x:v>50 或 50% 都表示 50%；一般格式數值 0.5 表示 0.5%。Excel 百分比格式依顯示比例換算，明細會列採用值。空白採 100%。</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="40" customHeight="1">
@@ -3286,7 +3286,7 @@
         <x:v>同時使用率(%)</x:v>
       </x:c>
       <x:c r="B113" s="1" t="str">
-        <x:v>瞬間同時需求的估算係數，填0~100；不是每小時運轉分鐘數。支路仍按額定負載。</x:v>
+        <x:v>50 或 50% 表示 50%；一般數值 0.5 表示 0.5%。Excel 百分比格式依顯示比例換算；不是每小時運轉比例。支路仍核全載。</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -5451,7 +5451,7 @@
         <x:v>同時使用率(%)</x:v>
       </x:c>
       <x:c r="B113" s="1" t="str">
-        <x:v>瞬間同時需求的估算係數，填0~100；不是每小時運轉分鐘數。支路仍按額定負載。</x:v>
+        <x:v>50 或 50% 表示 50%；一般數值 0.5 表示 0.5%。Excel 百分比格式依顯示比例換算；不是每小時運轉比例。支路仍核全載。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8125,7 +8125,7 @@
         <x:v>同時使用率(%)</x:v>
       </x:c>
       <x:c r="B113" s="1" t="str">
-        <x:v>瞬間同時需求的估算係數，填0~100；不是每小時運轉分鐘數。支路仍按額定負載。</x:v>
+        <x:v>50 或 50% 表示 50%；一般數值 0.5 表示 0.5%。Excel 百分比格式依顯示比例換算；不是每小時運轉比例。支路仍核全載。</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -10815,7 +10815,7 @@
         <x:v>同時使用率(%)</x:v>
       </x:c>
       <x:c r="B113" s="1" t="str">
-        <x:v>瞬間同時需求的估算係數，填0~100；不是每小時運轉分鐘數。支路仍按額定負載。</x:v>
+        <x:v>50 或 50% 表示 50%；一般數值 0.5 表示 0.5%。Excel 百分比格式依顯示比例換算；不是每小時運轉比例。支路仍核全載。</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -13065,7 +13065,7 @@
         <x:v>同時使用率(%)</x:v>
       </x:c>
       <x:c r="B113" s="1" t="str">
-        <x:v>瞬間同時需求的估算係數，填0~100；不是每小時運轉分鐘數。支路仍按額定負載。</x:v>
+        <x:v>50 或 50% 表示 50%；一般數值 0.5 表示 0.5%。Excel 百分比格式依顯示比例換算；不是每小時運轉比例。支路仍核全載。</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -15208,7 +15208,7 @@
         <x:v>同時使用率(%)</x:v>
       </x:c>
       <x:c r="B113" s="1" t="str">
-        <x:v>瞬間同時需求的估算係數，填0~100；不是每小時運轉分鐘數。支路仍按額定負載。</x:v>
+        <x:v>50 或 50% 表示 50%；一般數值 0.5 表示 0.5%。Excel 百分比格式依顯示比例換算；不是每小時運轉比例。支路仍核全載。</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -17780,7 +17780,7 @@
         <x:v>同時使用率(%)</x:v>
       </x:c>
       <x:c r="B113" s="1" t="str">
-        <x:v>瞬間同時需求的估算係數，填0~100；不是每小時運轉分鐘數。支路仍按額定負載。</x:v>
+        <x:v>50 或 50% 表示 50%；一般數值 0.5 表示 0.5%。Excel 百分比格式依顯示比例換算；不是每小時運轉比例。支路仍核全載。</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
